--- a/data/trans_orig/P36BPD07_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_R-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>664817</t>
+          <t>663898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>696005</t>
+          <t>695798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>910236</t>
+          <t>910719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>942182</t>
+          <t>940794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1586232</t>
+          <t>1585307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1630316</t>
+          <t>1626822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>49390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80371</t>
+          <t>81290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74694</t>
+          <t>74211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>103295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143885</t>
+          <t>144810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1635033</t>
+          <t>1636060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1705809</t>
+          <t>1706791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1600272</t>
+          <t>1596436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1667140</t>
+          <t>1661750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3251857</t>
+          <t>3254454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3352245</t>
+          <t>3351428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359600</t>
+          <t>358618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430376</t>
+          <t>429349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309785</t>
+          <t>315175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376653</t>
+          <t>380489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690088</t>
+          <t>690905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790476</t>
+          <t>787879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>460624</t>
+          <t>461889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>490591</t>
+          <t>491904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>469238</t>
+          <t>470021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>497469</t>
+          <t>498471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>939502</t>
+          <t>940812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>980756</t>
+          <t>980729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83153</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50503</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>77951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110993</t>
+          <t>111020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152247</t>
+          <t>150937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2787944</t>
+          <t>2783047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2870258</t>
+          <t>2870702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3003592</t>
+          <t>3000692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3081555</t>
+          <t>3079557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5818016</t>
+          <t>5819945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5942108</t>
+          <t>5932727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484115</t>
+          <t>483671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566429</t>
+          <t>571326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428271</t>
+          <t>430269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506234</t>
+          <t>509134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922091</t>
+          <t>931472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1046183</t>
+          <t>1044254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>375338</t>
+          <t>428348</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>356041</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394833</t>
+          <t>448288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>590708</t>
+          <t>635637</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>572220</t>
+          <t>613652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>607330</t>
+          <t>654709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>966046</t>
+          <t>1063986</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>941536</t>
+          <t>1033066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>992805</t>
+          <t>1092689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>137545</t>
+          <t>148046</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118050</t>
+          <t>128106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156842</t>
+          <t>168480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>164800</t>
+          <t>186401</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148178</t>
+          <t>167329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183288</t>
+          <t>208386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>334446</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275586</t>
+          <t>305743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>326855</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1651225</t>
+          <t>1504831</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1556257</t>
+          <t>1452632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1861818</t>
+          <t>1554756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1733945</t>
+          <t>1590934</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1656477</t>
+          <t>1550456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1865420</t>
+          <t>1633139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3385170</t>
+          <t>3095765</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3247355</t>
+          <t>3029565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3608655</t>
+          <t>3164882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>636316</t>
+          <t>722716</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425723</t>
+          <t>672791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731284</t>
+          <t>774915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499606</t>
+          <t>575468</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368131</t>
+          <t>533263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>577074</t>
+          <t>615946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1135922</t>
+          <t>1298184</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912437</t>
+          <t>1229067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1273737</t>
+          <t>1364384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,67 +3015,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>518837</t>
+          <t>578051</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>488756</t>
+          <t>554872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>539862</t>
+          <t>599716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>611963</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>590164</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>629158</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>83,49%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>554253</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>537435</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>571207</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1073091</t>
+          <t>1190014</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1038734</t>
+          <t>1159862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1102779</t>
+          <t>1218337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -3128,67 +3128,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>133536</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106761</t>
+          <t>111871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157867</t>
+          <t>156715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>121022</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103827</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>142821</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>16,51%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105003</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88049</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>121821</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>232788</t>
+          <t>254558</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203100</t>
+          <t>226235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267145</t>
+          <t>284710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2545401</t>
+          <t>2511231</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2446925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2764129</t>
+          <t>2566911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2878906</t>
+          <t>2838534</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2807040</t>
+          <t>2787246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3012357</t>
+          <t>2884112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5424306</t>
+          <t>5349765</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5292241</t>
+          <t>5270730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5665682</t>
+          <t>5426754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>901646</t>
+          <t>1004297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>682918</t>
+          <t>948617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>990645</t>
+          <t>1068603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>769409</t>
+          <t>882891</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635958</t>
+          <t>837313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>841275</t>
+          <t>934179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1671056</t>
+          <t>1887188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1429680</t>
+          <t>1810199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1803121</t>
+          <t>1966223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
